--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.71576881112989</v>
+        <v>10.51631243180861</v>
       </c>
       <c r="D2" t="n">
-        <v>50.79455844210879</v>
+        <v>8.254115746842679</v>
       </c>
       <c r="E2" t="n">
-        <v>6.541813466073528</v>
+        <v>1.063044688236948</v>
       </c>
       <c r="F2" t="n">
-        <v>1.103054870758303</v>
+        <v>0.1792464164982244</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.63214187898284</v>
+        <v>8.390223055334712</v>
       </c>
       <c r="D3" t="n">
-        <v>48.58844870059218</v>
+        <v>7.89562291384623</v>
       </c>
       <c r="E3" t="n">
-        <v>6.541813466073528</v>
+        <v>1.063044688236948</v>
       </c>
       <c r="F3" t="n">
-        <v>1.103054870758303</v>
+        <v>0.1792464164982244</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
